--- a/docs/inventario-2026-05/07-relatorios/outliers-cod-nao-digito.xlsx
+++ b/docs/inventario-2026-05/07-relatorios/outliers-cod-nao-digito.xlsx
@@ -499,22 +499,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X105000022</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MOLHO SHOYU TRADICIONAL</t>
+          <t>AZEITONA VERDE GORDAL</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1955.189</v>
+        <v>30144.537</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11054.63</v>
+        <v>43724.72</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>0</v>
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cod_nao_digito (produto arquivado X* ou fiscal)</t>
+          <t>tipo_produto=5 fora de (1,2,3,4) — sem mapeamento fiscal</t>
         </is>
       </c>
     </row>
@@ -567,22 +567,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>X105000022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE GORDAL</t>
+          <t>MOLHO SHOYU TRADICIONAL</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>30144.537</v>
+        <v>1955.189</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>43724.72</v>
+        <v>11054.63</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>tipo_produto=5 fora de (1,2,3,4) — sem mapeamento fiscal</t>
+          <t>cod_nao_digito (produto arquivado X* ou fiscal)</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>602000006</t>
+          <t>X104000016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BARRICAS</t>
+          <t>VINAGRE DE ALCOOL TRIPLO</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0</v>
@@ -696,29 +696,29 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>tipo_produto=6 fora de (1,2,3,4) — sem mapeamento fiscal</t>
+          <t>cod_nao_digito (produto arquivado X* ou fiscal)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X104000016</t>
+          <t>602000006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VINAGRE DE ALCOOL TRIPLO</t>
+          <t>BARRICAS</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>cod_nao_digito (produto arquivado X* ou fiscal)</t>
+          <t>tipo_produto=6 fora de (1,2,3,4) — sem mapeamento fiscal</t>
         </is>
       </c>
     </row>
